--- a/excel/support_cards.xlsx
+++ b/excel/support_cards.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="105">
   <si>
     <t>ID</t>
   </si>
@@ -33,15 +33,27 @@
     <t>サンプル</t>
   </si>
   <si>
+    <t>イベント1 種類</t>
+  </si>
+  <si>
     <t>イベント1 対象</t>
   </si>
   <si>
+    <t>イベント1 最大回数</t>
+  </si>
+  <si>
     <t>イベント1 値</t>
   </si>
   <si>
+    <t>イベント2 種類</t>
+  </si>
+  <si>
     <t>イベント2 対象</t>
   </si>
   <si>
+    <t>イベント2 最大回数</t>
+  </si>
+  <si>
     <t>イベント2 値</t>
   </si>
   <si>
@@ -135,6 +147,9 @@
     <t>○</t>
   </si>
   <si>
+    <t>初期評価</t>
+  </si>
+  <si>
     <t>Da</t>
   </si>
   <si>
@@ -156,9 +171,6 @@
     <t>VoSP終了時</t>
   </si>
   <si>
-    <t>初期評価</t>
-  </si>
-  <si>
     <t>sample_002</t>
   </si>
   <si>
@@ -306,7 +318,7 @@
     <t>・上記以外の効果種類は、同じ名前の行動回数（Voレッスン / Daレッスン / Viレッスン / VoSPレッスン / DaSPレッスン / ViSPレッスン / 授業 / おでかけ / 相談 / 強化 / 削除 / 活動支給 / 休む）で発動します。</t>
   </si>
   <si>
-    <t>・イベント効果1〜2 は、行動回数に関係なく1回だけ加算する値です。なければ空欄にしてください。</t>
+    <t>・イベント効果1〜2 は効果と同じ書き方（種類・対象・最大回数・値）で、計算方法も効果と同じです。なければ4列とも空欄にしてください。</t>
   </si>
   <si>
     <t>・サンプル列に ○ を付けたカードは、画面に「サンプル（ダミー）」として表示されます。実データには付けないでください。</t>
@@ -735,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH13"/>
+  <dimension ref="A1:AL13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -743,7 +755,9 @@
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="7" max="10" width="8" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="7" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
@@ -762,9 +776,12 @@
     <col min="31" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="7" customWidth="1"/>
     <col min="34" max="34" width="8" customWidth="1"/>
+    <col min="35" max="35" width="14" customWidth="1"/>
+    <col min="36" max="36" width="7" customWidth="1"/>
+    <col min="38" max="38" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -795,400 +812,421 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AG1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="O2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2">
+        <v>3</v>
+      </c>
+      <c r="R2">
+        <v>10</v>
+      </c>
+      <c r="S2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2">
+        <v>2</v>
+      </c>
+      <c r="V2">
+        <v>15</v>
+      </c>
+      <c r="W2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y2">
+        <v>2</v>
+      </c>
+      <c r="Z2">
+        <v>10</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>20</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG2">
+        <v>4</v>
+      </c>
+      <c r="AH2">
+        <v>8</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
         <v>40</v>
       </c>
-      <c r="H2">
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>10</v>
+      </c>
+      <c r="O3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
+        <v>9</v>
+      </c>
+      <c r="S3" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3">
+        <v>3</v>
+      </c>
+      <c r="V3">
+        <v>12</v>
+      </c>
+      <c r="W3" t="s">
+        <v>57</v>
+      </c>
+      <c r="X3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y3">
+        <v>2</v>
+      </c>
+      <c r="Z3">
+        <v>14</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC3">
+        <v>2</v>
+      </c>
+      <c r="AD3">
+        <v>10</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG3">
+        <v>1</v>
+      </c>
+      <c r="AH3">
         <v>20</v>
       </c>
-      <c r="K2" t="s">
+      <c r="AI3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
         <v>41</v>
       </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2">
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4">
         <v>3</v>
       </c>
-      <c r="N2">
+      <c r="R4">
         <v>10</v>
       </c>
-      <c r="O2" t="s">
+      <c r="S4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" t="s">
+        <v>50</v>
+      </c>
+      <c r="U4">
+        <v>2</v>
+      </c>
+      <c r="V4">
+        <v>12</v>
+      </c>
+      <c r="W4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4">
+        <v>2</v>
+      </c>
+      <c r="Z4">
+        <v>10</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC4">
+        <v>3</v>
+      </c>
+      <c r="AD4">
+        <v>6</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH4">
+        <v>40</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
         <v>43</v>
       </c>
-      <c r="P2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2">
-        <v>2</v>
-      </c>
-      <c r="R2">
-        <v>15</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="G5" t="s">
         <v>44</v>
       </c>
-      <c r="T2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2">
-        <v>2</v>
-      </c>
-      <c r="V2">
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5">
         <v>10</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
-      <c r="Z2">
-        <v>20</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC2">
-        <v>4</v>
-      </c>
-      <c r="AD2">
-        <v>8</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-      <c r="N3">
-        <v>9</v>
-      </c>
-      <c r="O3" t="s">
-        <v>52</v>
-      </c>
-      <c r="P3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3">
-        <v>3</v>
-      </c>
-      <c r="R3">
-        <v>12</v>
-      </c>
-      <c r="S3" t="s">
-        <v>53</v>
-      </c>
-      <c r="T3" t="s">
-        <v>42</v>
-      </c>
-      <c r="U3">
-        <v>2</v>
-      </c>
-      <c r="V3">
-        <v>14</v>
-      </c>
-      <c r="W3" t="s">
-        <v>54</v>
-      </c>
-      <c r="X3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y3">
-        <v>2</v>
-      </c>
-      <c r="Z3">
-        <v>10</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC3">
-        <v>1</v>
-      </c>
-      <c r="AD3">
-        <v>20</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-      <c r="N4">
-        <v>10</v>
-      </c>
-      <c r="O4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4">
-        <v>2</v>
-      </c>
-      <c r="R4">
-        <v>12</v>
-      </c>
-      <c r="S4" t="s">
-        <v>44</v>
-      </c>
-      <c r="T4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U4">
-        <v>2</v>
-      </c>
-      <c r="V4">
-        <v>10</v>
-      </c>
-      <c r="W4" t="s">
-        <v>59</v>
-      </c>
-      <c r="X4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y4">
-        <v>3</v>
-      </c>
-      <c r="Z4">
-        <v>6</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD4">
-        <v>40</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG4">
-        <v>1</v>
-      </c>
-      <c r="AH4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="K5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-      <c r="N5">
-        <v>8</v>
-      </c>
       <c r="O5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -1197,351 +1235,360 @@
         <v>8</v>
       </c>
       <c r="S5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5" t="s">
+        <v>47</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>8</v>
+      </c>
+      <c r="W5" t="s">
+        <v>48</v>
+      </c>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>10</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC5">
+        <v>2</v>
+      </c>
+      <c r="AD5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
         <v>43</v>
       </c>
-      <c r="T5" t="s">
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="O6" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <v>12</v>
+      </c>
+      <c r="S6" t="s">
+        <v>49</v>
+      </c>
+      <c r="T6" t="s">
+        <v>50</v>
+      </c>
+      <c r="U6">
+        <v>2</v>
+      </c>
+      <c r="V6">
+        <v>15</v>
+      </c>
+      <c r="W6" t="s">
+        <v>62</v>
+      </c>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6">
+        <v>3</v>
+      </c>
+      <c r="Z6">
+        <v>8</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC6">
+        <v>2</v>
+      </c>
+      <c r="AD6">
+        <v>10</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG6">
+        <v>2</v>
+      </c>
+      <c r="AH6">
+        <v>14</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="U5">
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7">
+        <v>30</v>
+      </c>
+      <c r="O7" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q7">
+        <v>4</v>
+      </c>
+      <c r="R7">
+        <v>10</v>
+      </c>
+      <c r="S7" t="s">
+        <v>63</v>
+      </c>
+      <c r="T7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>7</v>
+      </c>
+      <c r="W7" t="s">
+        <v>48</v>
+      </c>
+      <c r="X7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y7">
+        <v>2</v>
+      </c>
+      <c r="Z7">
+        <v>12</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AD7">
+        <v>10</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG7">
+        <v>2</v>
+      </c>
+      <c r="AH7">
+        <v>11</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="O8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8">
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <v>9</v>
+      </c>
+      <c r="S8" t="s">
+        <v>48</v>
+      </c>
+      <c r="T8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>12</v>
+      </c>
+      <c r="W8" t="s">
+        <v>49</v>
+      </c>
+      <c r="X8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y8">
         <v>1</v>
       </c>
-      <c r="V5">
+      <c r="Z8">
+        <v>18</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC8">
+        <v>2</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG8">
+        <v>2</v>
+      </c>
+      <c r="AH8">
+        <v>8</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9">
         <v>10</v>
       </c>
-      <c r="W5" t="s">
-        <v>53</v>
-      </c>
-      <c r="X5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y5">
-        <v>2</v>
-      </c>
-      <c r="Z5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-      <c r="N6">
-        <v>12</v>
-      </c>
-      <c r="O6" t="s">
-        <v>44</v>
-      </c>
-      <c r="P6" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6">
-        <v>2</v>
-      </c>
-      <c r="R6">
-        <v>15</v>
-      </c>
-      <c r="S6" t="s">
-        <v>58</v>
-      </c>
-      <c r="T6" t="s">
-        <v>40</v>
-      </c>
-      <c r="U6">
-        <v>3</v>
-      </c>
-      <c r="V6">
-        <v>8</v>
-      </c>
-      <c r="W6" t="s">
-        <v>41</v>
-      </c>
-      <c r="X6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y6">
-        <v>2</v>
-      </c>
-      <c r="Z6">
-        <v>10</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC6">
-        <v>2</v>
-      </c>
-      <c r="AD6">
-        <v>14</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH6">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7">
-        <v>30</v>
-      </c>
-      <c r="K7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
-      </c>
-      <c r="N7">
-        <v>10</v>
-      </c>
-      <c r="O7" t="s">
-        <v>59</v>
-      </c>
-      <c r="P7" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q7">
-        <v>3</v>
-      </c>
-      <c r="R7">
-        <v>7</v>
-      </c>
-      <c r="S7" t="s">
-        <v>43</v>
-      </c>
-      <c r="T7" t="s">
-        <v>45</v>
-      </c>
-      <c r="U7">
-        <v>2</v>
-      </c>
-      <c r="V7">
-        <v>12</v>
-      </c>
-      <c r="W7" t="s">
-        <v>54</v>
-      </c>
-      <c r="X7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y7">
-        <v>2</v>
-      </c>
-      <c r="Z7">
-        <v>10</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC7">
-        <v>2</v>
-      </c>
-      <c r="AD7">
-        <v>11</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-      <c r="N8">
-        <v>9</v>
-      </c>
-      <c r="O8" t="s">
-        <v>43</v>
-      </c>
-      <c r="P8" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <v>12</v>
-      </c>
-      <c r="S8" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" t="s">
-        <v>42</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>18</v>
-      </c>
-      <c r="W8" t="s">
-        <v>51</v>
-      </c>
-      <c r="X8" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y8">
-        <v>2</v>
-      </c>
-      <c r="Z8">
-        <v>7</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC8">
-        <v>2</v>
-      </c>
-      <c r="AD8">
-        <v>8</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH8">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="O9" t="s">
         <v>62</v>
       </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="K9" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
-      <c r="N9">
-        <v>7</v>
-      </c>
-      <c r="O9" t="s">
-        <v>54</v>
-      </c>
       <c r="P9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -1550,360 +1597,369 @@
         <v>7</v>
       </c>
       <c r="S9" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="T9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U9">
         <v>2</v>
       </c>
       <c r="V9">
+        <v>7</v>
+      </c>
+      <c r="W9" t="s">
+        <v>78</v>
+      </c>
+      <c r="X9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y9">
+        <v>2</v>
+      </c>
+      <c r="Z9">
         <v>6</v>
       </c>
-      <c r="W9" t="s">
-        <v>47</v>
-      </c>
-      <c r="X9" t="s">
+      <c r="AA9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="Z9">
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="O10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q10">
+        <v>4</v>
+      </c>
+      <c r="R10">
+        <v>11</v>
+      </c>
+      <c r="S10" t="s">
+        <v>57</v>
+      </c>
+      <c r="T10" t="s">
+        <v>45</v>
+      </c>
+      <c r="U10">
+        <v>2</v>
+      </c>
+      <c r="V10">
+        <v>13</v>
+      </c>
+      <c r="W10" t="s">
+        <v>46</v>
+      </c>
+      <c r="X10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y10">
+        <v>2</v>
+      </c>
+      <c r="Z10">
+        <v>10</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC10">
+        <v>2</v>
+      </c>
+      <c r="AD10">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG10">
+        <v>3</v>
+      </c>
+      <c r="AH10">
+        <v>7</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11">
+        <v>30</v>
+      </c>
+      <c r="O11" t="s">
+        <v>48</v>
+      </c>
+      <c r="P11" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q11">
+        <v>3</v>
+      </c>
+      <c r="R11">
+        <v>12</v>
+      </c>
+      <c r="S11" t="s">
         <v>75</v>
       </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10">
-        <v>20</v>
-      </c>
-      <c r="K10" t="s">
-        <v>52</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="T11" t="s">
+        <v>50</v>
+      </c>
+      <c r="U11">
+        <v>2</v>
+      </c>
+      <c r="V11">
+        <v>14</v>
+      </c>
+      <c r="W11" t="s">
+        <v>78</v>
+      </c>
+      <c r="X11" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y11">
+        <v>3</v>
+      </c>
+      <c r="Z11">
+        <v>8</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC11">
+        <v>2</v>
+      </c>
+      <c r="AD11">
+        <v>10</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
+      <c r="AH11">
+        <v>8</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" t="s">
+        <v>63</v>
+      </c>
+      <c r="P12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12">
+        <v>9</v>
+      </c>
+      <c r="S12" t="s">
+        <v>49</v>
+      </c>
+      <c r="T12" t="s">
+        <v>47</v>
+      </c>
+      <c r="U12">
+        <v>2</v>
+      </c>
+      <c r="V12">
+        <v>10</v>
+      </c>
+      <c r="W12" t="s">
+        <v>62</v>
+      </c>
+      <c r="X12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y12">
+        <v>2</v>
+      </c>
+      <c r="Z12">
+        <v>8</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC12">
+        <v>2</v>
+      </c>
+      <c r="AD12">
+        <v>9</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH12">
         <v>40</v>
       </c>
-      <c r="M10">
-        <v>4</v>
-      </c>
-      <c r="N10">
-        <v>11</v>
-      </c>
-      <c r="O10" t="s">
-        <v>53</v>
-      </c>
-      <c r="P10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
-      <c r="R10">
-        <v>13</v>
-      </c>
-      <c r="S10" t="s">
-        <v>41</v>
-      </c>
-      <c r="T10" t="s">
-        <v>45</v>
-      </c>
-      <c r="U10">
-        <v>2</v>
-      </c>
-      <c r="V10">
+      <c r="AI12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK12">
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13">
         <v>10</v>
       </c>
-      <c r="W10" t="s">
-        <v>44</v>
-      </c>
-      <c r="X10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y10">
-        <v>2</v>
-      </c>
-      <c r="Z10">
-        <v>12</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC10">
-        <v>3</v>
-      </c>
-      <c r="AD10">
+      <c r="O13" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q13">
+        <v>2</v>
+      </c>
+      <c r="R13">
         <v>7</v>
       </c>
-      <c r="AE10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11">
-        <v>30</v>
-      </c>
-      <c r="K11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" t="s">
-        <v>45</v>
-      </c>
-      <c r="M11">
-        <v>3</v>
-      </c>
-      <c r="N11">
-        <v>12</v>
-      </c>
-      <c r="O11" t="s">
-        <v>71</v>
-      </c>
-      <c r="P11" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
-      <c r="R11">
-        <v>14</v>
-      </c>
-      <c r="S11" t="s">
-        <v>74</v>
-      </c>
-      <c r="T11" t="s">
-        <v>45</v>
-      </c>
-      <c r="U11">
-        <v>3</v>
-      </c>
-      <c r="V11">
-        <v>8</v>
-      </c>
-      <c r="W11" t="s">
-        <v>53</v>
-      </c>
-      <c r="X11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y11">
-        <v>2</v>
-      </c>
-      <c r="Z11">
-        <v>10</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC11">
-        <v>2</v>
-      </c>
-      <c r="AD11">
-        <v>8</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH11">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" t="s">
-        <v>39</v>
-      </c>
-      <c r="K12" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" t="s">
-        <v>42</v>
-      </c>
-      <c r="M12">
-        <v>3</v>
-      </c>
-      <c r="N12">
-        <v>9</v>
-      </c>
-      <c r="O12" t="s">
-        <v>44</v>
-      </c>
-      <c r="P12" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q12">
-        <v>2</v>
-      </c>
-      <c r="R12">
-        <v>10</v>
-      </c>
-      <c r="S12" t="s">
-        <v>58</v>
-      </c>
-      <c r="T12" t="s">
-        <v>45</v>
-      </c>
-      <c r="U12">
-        <v>2</v>
-      </c>
-      <c r="V12">
-        <v>8</v>
-      </c>
-      <c r="W12" t="s">
-        <v>43</v>
-      </c>
-      <c r="X12" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y12">
-        <v>2</v>
-      </c>
-      <c r="Z12">
-        <v>9</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD12">
-        <v>40</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG12">
-        <v>1</v>
-      </c>
-      <c r="AH12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="S13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="K13" t="s">
-        <v>41</v>
-      </c>
-      <c r="L13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13">
-        <v>2</v>
-      </c>
-      <c r="N13">
-        <v>7</v>
-      </c>
-      <c r="O13" t="s">
-        <v>58</v>
-      </c>
-      <c r="P13" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q13">
-        <v>2</v>
-      </c>
-      <c r="R13">
-        <v>6</v>
-      </c>
-      <c r="S13" t="s">
-        <v>53</v>
-      </c>
       <c r="T13" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -1912,17 +1968,29 @@
         <v>6</v>
       </c>
       <c r="W13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="X13" t="s">
         <v>45</v>
       </c>
+      <c r="Y13">
+        <v>2</v>
+      </c>
       <c r="Z13">
+        <v>6</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD13">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="30">
+  <dataValidations count="34">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="AA2:AA1000">
       <formula1>リスト!$C$2:$C$18</formula1>
     </dataValidation>
@@ -1947,20 +2015,32 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="0以上の数値を入力してください" sqref="AH2:AH1000">
       <formula1>0</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="AI2:AI1000">
+      <formula1>リスト!$C$2:$C$18</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="AJ2:AJ1000">
+      <formula1>リスト!$B$2:$B$4</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="0以上の整数を入力してください" sqref="AK2:AK1000">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="0以上の数値を入力してください" sqref="AL2:AL1000">
+      <formula1>0</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「プラン」の一覧から選んでください" sqref="D2:D1000">
       <formula1>リスト!$A$2:$A$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「サンプル」の一覧から選んでください" sqref="F2:F1000">
       <formula1>リスト!$D$2:$D$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="G2:G1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="G2:G1000">
+      <formula1>リスト!$C$2:$C$18</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="H2:H1000">
       <formula1>リスト!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="0以上の数値を入力してください" sqref="H2:H1000">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="0以上の整数を入力してください" sqref="I2:I1000">
       <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="I2:I1000">
-      <formula1>リスト!$B$2:$B$4</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="0以上の数値を入力してください" sqref="J2:J1000">
       <formula1>0</formula1>
@@ -2029,10 +2109,10 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
         <v>5</v>
@@ -2040,108 +2120,108 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2160,67 +2240,67 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/excel/support_cards.xlsx
+++ b/excel/support_cards.xlsx
@@ -309,7 +309,7 @@
     <t>・今の計算式で表せない効果（パラメータ上昇量%アップ、条件付きの効果など）も空欄にしてください。</t>
   </si>
   <si>
-    <t>・固定加算の効果: 初期評価 … 行動回数に関係なく値を1回だけ加算します。最大回数は空欄にしてください。</t>
+    <t>・固定加算の効果: 初期評価 … 行動回数に関係なく値を1回だけ加算します。最大回数は 1 か空欄にしてください。</t>
   </si>
   <si>
     <t>・別の行動の回数で発動する効果: VoSP終了時（VoSPレッスンの回数） / DaSP終了時（DaSPレッスンの回数） / ViSP終了時（ViSPレッスンの回数）</t>
@@ -922,6 +922,9 @@
       <c r="H2" t="s">
         <v>45</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2">
         <v>20</v>
       </c>
@@ -1020,6 +1023,9 @@
       <c r="H3" t="s">
         <v>47</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="J3">
         <v>30</v>
       </c>
@@ -1219,6 +1225,9 @@
       <c r="H5" t="s">
         <v>47</v>
       </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="J5">
         <v>10</v>
       </c>
@@ -1296,6 +1305,9 @@
       <c r="H6" t="s">
         <v>47</v>
       </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
       <c r="J6">
         <v>20</v>
       </c>
@@ -1394,6 +1406,9 @@
       <c r="H7" t="s">
         <v>50</v>
       </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
       <c r="J7">
         <v>30</v>
       </c>
@@ -1581,6 +1596,9 @@
       <c r="H9" t="s">
         <v>47</v>
       </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
       <c r="J9">
         <v>10</v>
       </c>
@@ -1655,6 +1673,9 @@
       <c r="H10" t="s">
         <v>50</v>
       </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
       <c r="J10">
         <v>20</v>
       </c>
@@ -1753,6 +1774,9 @@
       <c r="H11" t="s">
         <v>45</v>
       </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
       <c r="J11">
         <v>30</v>
       </c>
@@ -1939,6 +1963,9 @@
       </c>
       <c r="H13" t="s">
         <v>45</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
       </c>
       <c r="J13">
         <v>10</v>

--- a/excel/support_cards.xlsx
+++ b/excel/support_cards.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="111">
   <si>
     <t>ID</t>
   </si>
@@ -201,7 +201,7 @@
     <t>SR</t>
   </si>
   <si>
-    <t>授業</t>
+    <t>授業・営業終了時</t>
   </si>
   <si>
     <t>Voレッスン</t>
@@ -240,7 +240,7 @@
     <t>【サンプル】ダミーカードG</t>
   </si>
   <si>
-    <t>活動支給</t>
+    <t>活動支給・差し入れ選択時</t>
   </si>
   <si>
     <t>sample_008</t>
@@ -285,13 +285,31 @@
     <t>効果種類</t>
   </si>
   <si>
-    <t>VoSPレッスン</t>
-  </si>
-  <si>
-    <t>DaSPレッスン</t>
-  </si>
-  <si>
-    <t>ViSPレッスン</t>
+    <t>試験・オーディション終了時</t>
+  </si>
+  <si>
+    <t>好調効果カード獲得時</t>
+  </si>
+  <si>
+    <t>好印象効果カード獲得時</t>
+  </si>
+  <si>
+    <t>やる気効果カード獲得時</t>
+  </si>
+  <si>
+    <t>集中効果カード獲得時</t>
+  </si>
+  <si>
+    <t>元気効果カード獲得時</t>
+  </si>
+  <si>
+    <t>強気効果カード獲得時</t>
+  </si>
+  <si>
+    <t>温存効果カード獲得時</t>
+  </si>
+  <si>
+    <t>全力効果カード獲得時</t>
   </si>
   <si>
     <t>サポートカードデータ 入力シート</t>
@@ -312,10 +330,10 @@
     <t>・固定加算の効果: 初期評価 … 行動回数に関係なく値を1回だけ加算します。最大回数は 1 か空欄にしてください。</t>
   </si>
   <si>
-    <t>・別の行動の回数で発動する効果: VoSP終了時（VoSPレッスンの回数） / DaSP終了時（DaSPレッスンの回数） / ViSP終了時（ViSPレッスンの回数）</t>
-  </si>
-  <si>
-    <t>・上記以外の効果種類は、同じ名前の行動回数（Voレッスン / Daレッスン / Viレッスン / VoSPレッスン / DaSPレッスン / ViSPレッスン / 授業 / おでかけ / 相談 / 強化 / 削除 / 活動支給 / 休む）で発動します。</t>
+    <t>・別の行動の回数で発動する効果: VoSP終了時（Voレッスンの回数） / DaSP終了時（Daレッスンの回数） / ViSP終了時（Viレッスンの回数）</t>
+  </si>
+  <si>
+    <t>・上記以外の効果種類は、同じ名前の行動回数（Voレッスン / Daレッスン / Viレッスン / 授業・営業終了時 / おでかけ / 相談 / 活動支給・差し入れ選択時 / 強化 / 削除 / 休む / 試験・オーディション終了時 / 好調効果カード獲得時 / 好印象効果カード獲得時 / やる気効果カード獲得時 / 集中効果カード獲得時 / 元気効果カード獲得時 / 強気効果カード獲得時 / 温存効果カード獲得時 / 全力効果カード獲得時）で発動します。</t>
   </si>
   <si>
     <t>・イベント効果1〜2 は効果と同じ書き方（種類・対象・最大回数・値）で、計算方法も効果と同じです。なければ4列とも空欄にしてください。</t>
@@ -755,28 +773,28 @@
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
     <col min="12" max="12" width="7" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
     <col min="16" max="16" width="7" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
     <col min="20" max="20" width="7" customWidth="1"/>
     <col min="22" max="22" width="8" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="23" max="23" width="24" customWidth="1"/>
     <col min="24" max="24" width="7" customWidth="1"/>
     <col min="26" max="26" width="8" customWidth="1"/>
-    <col min="27" max="27" width="14" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
     <col min="28" max="28" width="7" customWidth="1"/>
     <col min="30" max="30" width="8" customWidth="1"/>
-    <col min="31" max="31" width="14" customWidth="1"/>
+    <col min="31" max="31" width="24" customWidth="1"/>
     <col min="32" max="32" width="7" customWidth="1"/>
     <col min="34" max="34" width="8" customWidth="1"/>
-    <col min="35" max="35" width="14" customWidth="1"/>
+    <col min="35" max="35" width="24" customWidth="1"/>
     <col min="36" max="36" width="7" customWidth="1"/>
     <col min="38" max="38" width="8" customWidth="1"/>
   </cols>
@@ -2019,7 +2037,7 @@
   </sheetData>
   <dataValidations count="34">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="AA2:AA1000">
-      <formula1>リスト!$C$2:$C$18</formula1>
+      <formula1>リスト!$C$2:$C$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="AB2:AB1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2031,7 +2049,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="AE2:AE1000">
-      <formula1>リスト!$C$2:$C$18</formula1>
+      <formula1>リスト!$C$2:$C$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="AF2:AF1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2043,7 +2061,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="AI2:AI1000">
-      <formula1>リスト!$C$2:$C$18</formula1>
+      <formula1>リスト!$C$2:$C$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="AJ2:AJ1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2061,7 +2079,7 @@
       <formula1>リスト!$D$2:$D$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="G2:G1000">
-      <formula1>リスト!$C$2:$C$18</formula1>
+      <formula1>リスト!$C$2:$C$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="H2:H1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2073,7 +2091,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="K2:K1000">
-      <formula1>リスト!$C$2:$C$18</formula1>
+      <formula1>リスト!$C$2:$C$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="L2:L1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2085,7 +2103,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="O2:O1000">
-      <formula1>リスト!$C$2:$C$18</formula1>
+      <formula1>リスト!$C$2:$C$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="P2:P1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2097,7 +2115,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="S2:S1000">
-      <formula1>リスト!$C$2:$C$18</formula1>
+      <formula1>リスト!$C$2:$C$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="T2:T1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2109,7 +2127,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="W2:W1000">
-      <formula1>リスト!$C$2:$C$18</formula1>
+      <formula1>リスト!$C$2:$C$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="X2:X1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2128,7 +2146,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2183,71 +2201,101 @@
     </row>
     <row r="5" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2267,7 +2315,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2277,57 +2325,57 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/excel/support_cards.xlsx
+++ b/excel/support_cards.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="112">
   <si>
     <t>ID</t>
   </si>
@@ -285,6 +285,9 @@
     <t>効果種類</t>
   </si>
   <si>
+    <t>特別指導開始時</t>
+  </si>
+  <si>
     <t>試験・オーディション終了時</t>
   </si>
   <si>
@@ -333,7 +336,7 @@
     <t>・別の行動の回数で発動する効果: VoSP終了時（Voレッスンの回数） / DaSP終了時（Daレッスンの回数） / ViSP終了時（Viレッスンの回数）</t>
   </si>
   <si>
-    <t>・上記以外の効果種類は、同じ名前の行動回数（Voレッスン / Daレッスン / Viレッスン / 授業・営業終了時 / おでかけ / 相談 / 活動支給・差し入れ選択時 / 強化 / 削除 / 休む / 試験・オーディション終了時 / 好調効果カード獲得時 / 好印象効果カード獲得時 / やる気効果カード獲得時 / 集中効果カード獲得時 / 元気効果カード獲得時 / 強気効果カード獲得時 / 温存効果カード獲得時 / 全力効果カード獲得時）で発動します。</t>
+    <t>・上記以外の効果種類は、同じ名前の行動回数（Voレッスン / Daレッスン / Viレッスン / 授業・営業終了時 / おでかけ / 相談 / 活動支給・差し入れ選択時 / 強化 / 削除 / 休む / 特別指導開始時 / 試験・オーディション終了時 / 好調効果カード獲得時 / 好印象効果カード獲得時 / やる気効果カード獲得時 / 集中効果カード獲得時 / 元気効果カード獲得時 / 強気効果カード獲得時 / 温存効果カード獲得時 / 全力効果カード獲得時）で発動します。</t>
   </si>
   <si>
     <t>・イベント効果1〜2 は効果と同じ書き方（種類・対象・最大回数・値）で、計算方法も効果と同じです。なければ4列とも空欄にしてください。</t>
@@ -2037,7 +2040,7 @@
   </sheetData>
   <dataValidations count="34">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="AA2:AA1000">
-      <formula1>リスト!$C$2:$C$24</formula1>
+      <formula1>リスト!$C$2:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="AB2:AB1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2049,7 +2052,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="AE2:AE1000">
-      <formula1>リスト!$C$2:$C$24</formula1>
+      <formula1>リスト!$C$2:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="AF2:AF1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2061,7 +2064,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="AI2:AI1000">
-      <formula1>リスト!$C$2:$C$24</formula1>
+      <formula1>リスト!$C$2:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="AJ2:AJ1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2079,7 +2082,7 @@
       <formula1>リスト!$D$2:$D$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="G2:G1000">
-      <formula1>リスト!$C$2:$C$24</formula1>
+      <formula1>リスト!$C$2:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="H2:H1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2091,7 +2094,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="K2:K1000">
-      <formula1>リスト!$C$2:$C$24</formula1>
+      <formula1>リスト!$C$2:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="L2:L1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2103,7 +2106,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="O2:O1000">
-      <formula1>リスト!$C$2:$C$24</formula1>
+      <formula1>リスト!$C$2:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="P2:P1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2115,7 +2118,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="S2:S1000">
-      <formula1>リスト!$C$2:$C$24</formula1>
+      <formula1>リスト!$C$2:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="T2:T1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2127,7 +2130,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「効果種類」の一覧から選んでください" sqref="W2:W1000">
-      <formula1>リスト!$C$2:$C$24</formula1>
+      <formula1>リスト!$C$2:$C$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="入力エラー" error="「対象」の一覧から選んでください" sqref="X2:X1000">
       <formula1>リスト!$B$2:$B$4</formula1>
@@ -2146,7 +2149,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2281,21 +2284,26 @@
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2315,7 +2323,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2325,57 +2333,57 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/excel/support_cards.xlsx
+++ b/excel/support_cards.xlsx
@@ -2106,7 +2106,7 @@
     <t>・固定加算の効果: 初期評価 … 行動回数に関係なく値を1回だけ加算します。最大回数は 1 か空欄にしてください。</t>
   </si>
   <si>
-    <t>・別の行動の回数で発動する効果: SPレッスン（Vo・Da・Viレッスンの合計回数） / VoSP終了時（Voレッスンの回数） / DaSP終了時（Daレッスンの回数） / ViSP終了時（Viレッスンの回数） / スキル獲得時（各効果カード獲得時の合計回数）</t>
+    <t>・別の行動の回数で発動する効果: SPレッスン（対象パラメータのレッスン回数（Vo→Voレッスン、Da→Daレッスン、Vi→Viレッスン）） / VoSP終了時（Voレッスンの回数） / DaSP終了時（Daレッスンの回数） / ViSP終了時（Viレッスンの回数） / スキル獲得時（各効果カード獲得時の合計回数）</t>
   </si>
   <si>
     <t>・上記以外の効果種類は、同じ名前の行動回数（Voレッスン / Daレッスン / Viレッスン / 授業・営業終了時 / おでかけ / 相談 / 活動支給・差し入れ選択時 / 休む / 特別指導開始時 / 試験・オーディション終了時 / Pアイテム獲得時 / Pドリンク獲得時 / Pドリンク交換時 / スキル強化時 / スキル削除時 / スキルカスタム時 / スキルチェンジ時 / スキル（SSR）獲得時 / アクティブカード獲得時 / メンタルカード獲得時 / アクティブカード強化時 / メンタルカード強化時 / 好調効果カード獲得時 / 好印象効果カード獲得時 / やる気効果カード獲得時 / 集中効果カード獲得時 / 元気効果カード獲得時 / 強気効果カード獲得時 / 温存効果カード獲得時 / 全力効果カード獲得時）で発動します。</t>
